--- a/src/Tests/Samples.HiddenRow.verified.xlsx
+++ b/src/Tests/Samples.HiddenRow.verified.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="2000" yWindow="4120" windowWidth="30960" windowHeight="12120" activeTab="0"/>
+    <workbookView xWindow="2000" yWindow="4120" windowWidth="30960" windowHeight="12120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="DeterministicId5"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="DeterministicId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>First Name</t>
   </si>
@@ -112,13 +113,16 @@
   </si>
   <si>
     <t>DateTime_3</t>
+  </si>
+  <si>
+    <t>Evaluation Only. Created with Aspose.Cells for .NET. Copyright 2003 - 2026 Aspose Pty Ltd.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -139,6 +143,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -171,7 +183,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment/>
     </xf>
@@ -186,6 +198,10 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -797,4 +813,19 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>